--- a/06_Figures/S01_Volcano/c_data/s01_volcano.xlsx
+++ b/06_Figures/S01_Volcano/c_data/s01_volcano.xlsx
@@ -359,7 +359,7 @@
     <t>set_tests</t>
   </si>
   <si>
-    <t>03_Pathway_Enrichment/02_Contrasts/c_data/set_tests.rds</t>
+    <t>03_Pathways/03_Contrasts/c_data/set_tests.rds</t>
   </si>
   <si>
     <t>52c365ae84d1f5f25d3e280360d861dd</t>
